--- a/docs/Property-Import-Template.xlsx
+++ b/docs/Property-Import-Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="223">
   <si>
     <t>Field</t>
   </si>
@@ -72,6 +72,12 @@
     <t>Google Maps Link</t>
   </si>
   <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
     <t>Distance from Metro</t>
   </si>
   <si>
@@ -153,6 +159,9 @@
     <t>Built Up Area (In Sq. Ft.)</t>
   </si>
   <si>
+    <t>Floor Plan Image Link</t>
+  </si>
+  <si>
     <t>Amenities (Yes/No)</t>
   </si>
   <si>
@@ -309,7 +318,13 @@
     <t>Plot 4, Sector 10, Greater Noida West, UP 201306</t>
   </si>
   <si>
-    <t>https://maps.google.com/?q=...</t>
+    <t>https://maps.google.com/?q=28.5921,77.4400</t>
+  </si>
+  <si>
+    <t>28.5921</t>
+  </si>
+  <si>
+    <t>77.4400</t>
   </si>
   <si>
     <t>5 min</t>
@@ -435,6 +450,15 @@
     <t>2350</t>
   </si>
   <si>
+    <t>https://.../3bhk-plan.jpg</t>
+  </si>
+  <si>
+    <t>https://.../4bhk-plan.jpg</t>
+  </si>
+  <si>
+    <t>https://.../4bhks-plan.jpg</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
@@ -507,19 +531,13 @@
     <t>1 file = 1 property</t>
   </si>
   <si>
-    <t>For 10 projects, make 10 copies of this file. Up to 20 files can be uploaded together.</t>
+    <t>For 10 projects, make 10 copies. Up to 20 files can be uploaded together, each under 10 MB.</t>
   </si>
   <si>
     <t>Fill the first sheet</t>
   </si>
   <si>
-    <t>Only “Property Data” is read. The other two sheets are for reference and are ignored.</t>
-  </si>
-  <si>
-    <t>Save as .xlsx</t>
-  </si>
-  <si>
-    <t>Each file must stay under 10 MB.</t>
+    <t>Only “Property Data” is read. The other two sheets are reference and are ignored.</t>
   </si>
   <si>
     <t>Column A</t>
@@ -531,7 +549,7 @@
     <t>Column B</t>
   </si>
   <si>
-    <t>The value. Leave blank if unknown — blanks are skipped, they do not break anything.</t>
+    <t>The value. Leave blank if unknown — blanks are skipped and break nothing.</t>
   </si>
   <si>
     <t>Compulsory</t>
@@ -549,7 +567,7 @@
     <t>Nothing to the right</t>
   </si>
   <si>
-    <t>Do not add notes or extra columns beside a row — they are read as data.</t>
+    <t>Never put a note or an extra column beside a value — it is read as data.</t>
   </si>
   <si>
     <t>Rows using several columns</t>
@@ -558,19 +576,19 @@
     <t>Tower rows</t>
   </si>
   <si>
-    <t>Total Towers, Ceiling Height, Total Floor, Lift, Units Per Floor, Total Units In Tower.</t>
+    <t>Total Towers · Ceiling Height · Total Floor · Lift · Units Per Floor · Total Units In Tower</t>
   </si>
   <si>
     <t>Unit rows</t>
   </si>
   <si>
-    <t>Units Category, Saleable Area, Carpet Area, Balcony Area, Built Up Area.</t>
+    <t>Units Category · Saleable Area · Carpet Area · Balcony Area · Built Up Area · Floor Plan Image Link</t>
   </si>
   <si>
     <t>How</t>
   </si>
   <si>
-    <t>First tower/unit in column B, second in C, third in D… Columns must line up: column C of Units Category belongs with column C of Saleable Area.</t>
+    <t>First tower/unit in column B, second in C, third in D… The columns must line up: column C of Units Category belongs with column C of Saleable Area and column C of Floor Plan Image Link.</t>
   </si>
   <si>
     <t>Value formats</t>
@@ -582,6 +600,12 @@
     <t>FULL RUPEES. 1.25 Cr → 12500000.  85 Lakh → 8500000.  Do not write “Cr” or “Lakh”.</t>
   </si>
   <si>
+    <t>Latitude / Longitude</t>
+  </si>
+  <si>
+    <t>Decimal degrees, e.g. 28.5921 and 77.4400. Both are needed. Open the project in Google Maps, right-click the pin, and copy the two numbers. Without them the project cannot appear on the map or in the “near me” search.</t>
+  </si>
+  <si>
     <t>Distances</t>
   </si>
   <si>
@@ -606,13 +630,25 @@
     <t>“40” or “40+” — both are kept as written.</t>
   </si>
   <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Any public https link. Images must open directly, not through a preview page.</t>
+  </si>
+  <si>
+    <t>Why it matters</t>
+  </si>
+  <si>
+    <t>This decides whether the project shows as an Apartment, Villa, Plot or Builder Floor across the site and in comparisons. Write one of those four; anything unrecognised is treated as Apartment.</t>
+  </si>
+  <si>
     <t>Amenities</t>
   </si>
   <si>
     <t>Add your own</t>
   </si>
   <si>
-    <t>Any extra amenity can be a new row under Amenities. Unknown ones are still imported and shown on the property page.</t>
+    <t>Any extra amenity can be a new row. Unknown ones are still imported and shown on the property page.</t>
   </si>
   <si>
     <t>These eight filter the site</t>
@@ -624,7 +660,7 @@
     <t>Spell them exactly</t>
   </si>
   <si>
-    <t>Write “Gym”, not “Gymnasium”. Only the exact name is picked up by the website filter.</t>
+    <t>Write “Gym”, not “Gymnasium”. Only the exact name is picked up by the filter.</t>
   </si>
   <si>
     <t>Good to know</t>
@@ -1063,12 +1099,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="7" width="22" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="4" width="26" customWidth="1"/>
+    <col min="5" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1197,18 +1234,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1227,18 +1264,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="33" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1312,23 +1349,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="52" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1392,23 +1429,23 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="69" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1417,23 +1454,23 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="75" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1447,23 +1484,23 @@
         <v>72</v>
       </c>
     </row>
-    <row r="79" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="82" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1477,23 +1514,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="89" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1505,6 +1542,21 @@
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1515,12 +1567,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="7" width="22" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="4" width="26" customWidth="1"/>
+    <col min="5" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1556,7 +1609,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1564,7 +1617,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1572,7 +1625,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1580,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1588,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1596,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1604,7 +1657,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1612,7 +1665,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1620,7 +1673,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1628,7 +1681,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1641,7 +1694,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1649,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1657,7 +1710,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1665,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1673,7 +1726,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1681,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1689,7 +1742,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1697,28 +1750,28 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1726,7 +1779,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1734,7 +1787,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1742,28 +1795,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B33" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1771,7 +1824,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1779,7 +1832,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1787,34 +1840,22 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1826,10 +1867,10 @@
         <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,13 +1878,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1865,13 +1906,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1882,7 +1923,7 @@
         <v>125</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
         <v>127</v>
@@ -1896,10 +1937,10 @@
         <v>128</v>
       </c>
       <c r="C44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44" t="s">
         <v>129</v>
-      </c>
-      <c r="D44" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1907,13 +1948,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" t="s">
         <v>131</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>132</v>
-      </c>
-      <c r="D45" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1921,13 +1962,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
         <v>134</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>135</v>
-      </c>
-      <c r="D46" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1935,42 +1976,60 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" t="s">
         <v>137</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>138</v>
       </c>
-      <c r="D47" t="s">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B52" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1978,7 +2037,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1986,7 +2045,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1994,7 +2053,7 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2002,7 +2061,7 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2069,7 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2018,7 +2077,7 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2026,7 +2085,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2034,7 +2093,7 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2042,7 +2101,7 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2050,7 +2109,7 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2058,7 +2117,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2066,36 +2125,36 @@
         <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>62</v>
+      </c>
+      <c r="B65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B69" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2103,36 +2162,36 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>67</v>
+      </c>
+      <c r="B71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B74" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B75" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2140,7 +2199,7 @@
         <v>71</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2148,36 +2207,36 @@
         <v>72</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>73</v>
+      </c>
+      <c r="B78" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>75</v>
-      </c>
-      <c r="B81" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B82" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2185,7 +2244,7 @@
         <v>77</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2193,36 +2252,36 @@
         <v>78</v>
       </c>
       <c r="B84" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>79</v>
+      </c>
+      <c r="B85" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B86" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>81</v>
-      </c>
-      <c r="B88" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B89" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2230,7 +2289,7 @@
         <v>83</v>
       </c>
       <c r="B90" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2238,7 +2297,31 @@
         <v>84</v>
       </c>
       <c r="B91" t="s">
-        <v>161</v>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>86</v>
+      </c>
+      <c r="B93" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>87</v>
+      </c>
+      <c r="B94" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2249,12 +2332,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="78" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="82" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2262,7 +2345,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2273,10 +2356,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2284,10 +2367,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2295,10 +2378,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2306,10 +2389,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2317,10 +2400,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2328,10 +2411,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2339,32 +2422,32 @@
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>178</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2</v>
+      <c r="B11" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2372,10 +2455,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2383,32 +2466,32 @@
         <v>2</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" t="s">
-        <v>2</v>
+      <c r="B16" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2416,10 +2499,10 @@
         <v>2</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2427,10 +2510,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2438,10 +2521,10 @@
         <v>2</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2449,10 +2532,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2460,32 +2543,32 @@
         <v>2</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>199</v>
+      <c r="B24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2493,32 +2576,32 @@
         <v>2</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2</v>
+      <c r="B28" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2526,10 +2609,10 @@
         <v>2</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2537,21 +2620,54 @@
         <v>2</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>210</v>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
